--- a/data/trans_camb/P57_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P57_R2-Provincia-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 3,69</t>
+          <t>-14,41; 3,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,84; -1,81</t>
+          <t>-14,95; -3,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -1,0</t>
+          <t>-12,26; -0,63</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 13,57</t>
+          <t>-42,95; 13,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-51,33; -8,2</t>
+          <t>-50,07; -13,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,48; -3,45</t>
+          <t>-40,08; -2,52</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,9; 44,05</t>
+          <t>30,56; 44,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,75; 41,19</t>
+          <t>30,1; 41,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,06; 40,93</t>
+          <t>32,43; 41,26</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,13; 139,65</t>
+          <t>80,55; 137,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,45; 147,92</t>
+          <t>84,55; 145,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,45; 133,16</t>
+          <t>89,8; 133,0</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,21; 25,32</t>
+          <t>9,79; 25,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 16,67</t>
+          <t>3,44; 16,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,49; 18,66</t>
+          <t>8,24; 18,38</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30,08; 95,09</t>
+          <t>27,18; 92,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,55; 66,65</t>
+          <t>11,38; 68,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,09; 68,72</t>
+          <t>25,77; 67,9</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 9,16</t>
+          <t>-8,15; 8,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 7,44</t>
+          <t>-16,37; 7,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 5,43</t>
+          <t>-12,29; 5,19</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 25,01</t>
+          <t>-18,75; 23,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,02; 21,8</t>
+          <t>-45,48; 22,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,27; 14,6</t>
+          <t>-30,2; 14,63</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,1; 32,69</t>
+          <t>16,02; 33,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,7; 30,09</t>
+          <t>17,43; 31,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19,09; 29,24</t>
+          <t>19,14; 29,16</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>82,04; 277,55</t>
+          <t>82,96; 289,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>107,38; 333,37</t>
+          <t>110,61; 382,02</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112,87; 272,55</t>
+          <t>118,09; 268,99</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 7,67</t>
+          <t>-10,31; 7,3</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 15,52</t>
+          <t>-0,35; 14,77</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 8,83</t>
+          <t>-2,18; 8,77</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 16,63</t>
+          <t>-17,81; 16,08</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 39,1</t>
+          <t>-0,97; 35,67</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 19,6</t>
+          <t>-4,24; 19,93</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>8,85; 21,69</t>
+          <t>9,34; 21,17</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 15,43</t>
+          <t>-10,98; 15,4</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 15,5</t>
+          <t>-5,69; 15,74</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>27,82; 79,04</t>
+          <t>28,26; 78,02</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-51,13; 61,37</t>
+          <t>-41,07; 61,15</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-31,21; 57,04</t>
+          <t>-18,22; 58,86</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>20,09; 62,97</t>
+          <t>19,81; 60,77</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>12,6; 21,23</t>
+          <t>13,02; 21,44</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>18,54; 48,47</t>
+          <t>18,42; 48,29</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>97,38; 355,98</t>
+          <t>94,15; 328,07</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>70,48; 150,45</t>
+          <t>70,86; 149,51</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>99,74; 295,56</t>
+          <t>99,73; 282,02</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>15,8; 32,13</t>
+          <t>15,76; 31,46</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>4,86; 15,1</t>
+          <t>4,29; 14,96</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12,05; 22,01</t>
+          <t>12,08; 22,04</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>51,38; 107,58</t>
+          <t>51,28; 108,38</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>18,02; 58,73</t>
+          <t>17,91; 58,37</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>42,34; 79,69</t>
+          <t>42,32; 78,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P57_R2-Provincia-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-5,67</t>
+          <t>-7,83</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-8,62</t>
+          <t>-6,79</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-7,01</t>
+          <t>-7,32</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 3,69</t>
+          <t>-15,33; 0,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,95; -3,15</t>
+          <t>-12,9; -0,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,26; -0,63</t>
+          <t>-12,24; -2,49</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-18,22%</t>
+          <t>-25,15%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-34,16%</t>
+          <t>-26,91%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-24,85%</t>
+          <t>-25,96%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,95; 13,14</t>
+          <t>-44,41; -0,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,07; -13,3</t>
+          <t>-45,0; -0,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-40,08; -2,52</t>
+          <t>-39,43; -9,39</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>37,92</t>
+          <t>38,05</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>35,82</t>
+          <t>36,25</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36,92</t>
+          <t>37,15</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,56; 44,01</t>
+          <t>31,22; 44,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,1; 41,6</t>
+          <t>30,45; 41,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,43; 41,26</t>
+          <t>33,18; 41,31</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>108,39%</t>
+          <t>108,76%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>111,86%</t>
+          <t>113,21%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110,3%</t>
+          <t>111,0%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,55; 137,97</t>
+          <t>80,84; 140,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,55; 145,53</t>
+          <t>82,43; 148,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,8; 133,0</t>
+          <t>92,17; 134,8</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17,61</t>
+          <t>16,86</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9,93</t>
+          <t>10,16</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,56</t>
+          <t>13,28</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,79; 25,07</t>
+          <t>9,6; 23,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 16,62</t>
+          <t>3,62; 16,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 18,38</t>
+          <t>8,11; 18,58</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,18; 92,33</t>
+          <t>27,76; 87,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,38; 68,43</t>
+          <t>11,03; 65,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,77; 67,9</t>
+          <t>24,92; 70,44</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>5,96</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,08</t>
+          <t>3,96</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 8,85</t>
+          <t>-6,53; 11,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 7,68</t>
+          <t>-1,22; 12,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 5,19</t>
+          <t>-1,51; 9,97</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-0,1%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-7,38%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-5,51%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 23,54</t>
+          <t>-15,09; 29,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,48; 22,5</t>
+          <t>-3,24; 40,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,2; 14,63</t>
+          <t>-3,84; 28,39</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>24,83</t>
+          <t>25,26</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>24,25</t>
+          <t>23,89</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24,42</t>
+          <t>24,48</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,02; 33,06</t>
+          <t>17,42; 33,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,43; 31,2</t>
+          <t>17,0; 29,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19,14; 29,16</t>
+          <t>19,68; 29,22</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>160,86%</t>
+          <t>163,68%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>206,58%</t>
+          <t>203,48%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>180,12%</t>
+          <t>180,63%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>82,96; 289,02</t>
+          <t>86,32; 277,3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>110,61; 382,02</t>
+          <t>104,1; 358,76</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118,09; 268,99</t>
+          <t>122,77; 265,8</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-2,07</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7,26</t>
+          <t>6,75</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,15</t>
+          <t>2,38</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 7,3</t>
+          <t>-10,54; 5,81</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 14,77</t>
+          <t>-1,85; 14,23</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 8,77</t>
+          <t>-3,98; 7,79</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1,98%</t>
+          <t>-4,05%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 16,08</t>
+          <t>-19,04; 12,42</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 35,67</t>
+          <t>-3,66; 35,97</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 19,93</t>
+          <t>-7,64; 17,41</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>15,17</t>
+          <t>14,77</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>4,04</t>
+          <t>13,49</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8,54</t>
+          <t>14,09</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>9,34; 21,17</t>
+          <t>9,42; 20,32</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 15,4</t>
+          <t>8,93; 18,02</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 15,74</t>
+          <t>10,4; 17,43</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>50,94%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>28,26; 78,02</t>
+          <t>29,56; 75,69</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 61,15</t>
+          <t>31,53; 77,02</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 58,86</t>
+          <t>35,67; 68,8</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>37,06</t>
+          <t>21,9</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>17,23</t>
+          <t>17,16</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>28,73</t>
+          <t>19,5</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>19,81; 60,77</t>
+          <t>17,25; 26,73</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>13,02; 21,44</t>
+          <t>13,02; 21,2</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>18,42; 48,29</t>
+          <t>16,16; 22,62</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>185,41%</t>
+          <t>109,56%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>107,21%</t>
+          <t>106,75%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>159,85%</t>
+          <t>108,48%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>94,15; 328,07</t>
+          <t>77,4; 151,47</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>70,86; 149,51</t>
+          <t>70,94; 151,29</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>99,73; 282,02</t>
+          <t>83,07; 135,97</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>20,29</t>
+          <t>16,05</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>11,62</t>
+          <t>14,92</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>15,83</t>
+          <t>15,46</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>15,76; 31,46</t>
+          <t>13,37; 18,51</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>4,29; 14,96</t>
+          <t>12,95; 17,03</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12,08; 22,04</t>
+          <t>13,87; 17,16</t>
         </is>
       </c>
     </row>
@@ -1362,17 +1362,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>51,28; 108,38</t>
+          <t>42,61; 63,83</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>17,91; 58,37</t>
+          <t>46,78; 67,68</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>42,32; 78,95</t>
+          <t>47,31; 62,93</t>
         </is>
       </c>
     </row>
